--- a/artfynd/A 14234-2024 artfynd.xlsx
+++ b/artfynd/A 14234-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,72 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96711529</v>
+        <v>135518462</v>
       </c>
       <c r="B2" t="n">
-        <v>109866</v>
+        <v>58061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220228</v>
+        <v>102626</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Häggen, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499095</v>
+        <v>499044</v>
       </c>
       <c r="R2" t="n">
-        <v>6575791</v>
+        <v>6575757</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,24 +762,14 @@
           <t>Tysslinge</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Öre-0070</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca 680 plantor strax öster om husen i Häggen på båda sidor om vägen. 20 plantor lite längre österut (6577720, 1454160).</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,38 +778,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägkant.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnel Gustafson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnel Gustafson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134141111</v>
+        <v>135518511</v>
       </c>
       <c r="B3" t="n">
-        <v>109947</v>
+        <v>43224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,45 +807,62 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220228</v>
+        <v>201028</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Häggen, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498999</v>
+        <v>499069</v>
       </c>
       <c r="R3" t="n">
-        <v>6575739</v>
+        <v>6575774</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,17 +886,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>riklig</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +906,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Dike</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>vägdike</t>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>åkervädd</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Knautia arvensis</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Blomma på levande ört</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Flower on living herb/grass # Knautia arvensis</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134141104</v>
+        <v>96711529</v>
       </c>
       <c r="B4" t="n">
-        <v>110159</v>
+        <v>109866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,16 +955,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,19 +974,15 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>700</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -976,13 +991,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498999</v>
+        <v>499095</v>
       </c>
       <c r="R4" t="n">
-        <v>6575739</v>
+        <v>6575791</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,14 +1019,24 @@
           <t>Tysslinge</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Öre-0070</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2021-06-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 680 plantor strax öster om husen i Häggen på båda sidor om vägen. 20 plantor lite längre österut (6577720, 1454160).</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,28 +1049,272 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Dike</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>vägdike</t>
+          <t>Vägkant.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Gunnel Gustafson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gunnel Gustafson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134141111</v>
+      </c>
+      <c r="B5" t="n">
+        <v>109947</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Häggen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>498999</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6575739</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Dike</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>vägdike</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Michael Andersson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Michael Andersson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134141104</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Häggen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>498999</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6575739</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Dike</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>vägdike</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14234-2024 artfynd.xlsx
+++ b/artfynd/A 14234-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135518462</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -941,6 +951,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135518511</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1070,6 +1085,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96711529</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1191,6 +1211,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134141111</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1315,8 +1340,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134141104</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 14234-2024 artfynd.xlsx
+++ b/artfynd/A 14234-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135518462</v>
       </c>
       <c r="B2" t="n">
-        <v>58061</v>
+        <v>58066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>135518511</v>
       </c>
       <c r="B3" t="n">
-        <v>43224</v>
+        <v>43229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14234-2024 artfynd.xlsx
+++ b/artfynd/A 14234-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,60 +680,72 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96711529</v>
+        <v>135518462</v>
       </c>
       <c r="B2" t="n">
-        <v>109866</v>
+        <v>58066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220228</v>
+        <v>102626</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Häggen, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499095</v>
+        <v>499044</v>
       </c>
       <c r="R2" t="n">
-        <v>6575791</v>
+        <v>6575757</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,24 +767,14 @@
           <t>Tysslinge</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Öre-0070</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca 680 plantor strax öster om husen i Häggen på båda sidor om vägen. 20 plantor lite längre österut (6577720, 1454160).</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,43 +783,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägkant.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnel Gustafson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnel Gustafson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96711529</t>
+          <t>https://artportalen.se/Sighting/135518462</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134141111</v>
+        <v>135518511</v>
       </c>
       <c r="B3" t="n">
-        <v>109947</v>
+        <v>43229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,45 +817,62 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220228</v>
+        <v>201028</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Häggen, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498999</v>
+        <v>499069</v>
       </c>
       <c r="R3" t="n">
-        <v>6575739</v>
+        <v>6575774</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,17 +896,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>riklig</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,12 +916,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Dike</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>vägdike</t>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>åkervädd</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Knautia arvensis</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Blomma på levande ört</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Flower on living herb/grass # Knautia arvensis</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,16 +953,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134141111</t>
+          <t>https://artportalen.se/Sighting/135518511</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134141104</v>
+        <v>96711529</v>
       </c>
       <c r="B4" t="n">
-        <v>110159</v>
+        <v>109866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,16 +970,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -970,19 +989,15 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>700</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -991,13 +1006,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498999</v>
+        <v>499095</v>
       </c>
       <c r="R4" t="n">
-        <v>6575739</v>
+        <v>6575791</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1019,14 +1034,24 @@
           <t>Tysslinge</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Öre-0070</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2021-06-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 680 plantor strax öster om husen i Häggen på båda sidor om vägen. 20 plantor lite längre österut (6577720, 1454160).</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,29 +1064,283 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Dike</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>vägdike</t>
+          <t>Vägkant.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Gunnel Gustafson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gunnel Gustafson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96711529</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134141111</v>
+      </c>
+      <c r="B5" t="n">
+        <v>109947</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Häggen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>498999</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6575739</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Dike</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>vägdike</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Michael Andersson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Michael Andersson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr">
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134141111</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134141104</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Häggen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>498999</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6575739</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Dike</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>vägdike</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134141104</t>
         </is>
@@ -1072,6 +1351,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14234-2024 artfynd.xlsx
+++ b/artfynd/A 14234-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135518462</v>
       </c>
       <c r="B2" t="n">
-        <v>58066</v>
+        <v>58068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>135518511</v>
       </c>
       <c r="B3" t="n">
-        <v>43229</v>
+        <v>43231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
